--- a/client/public/Shakl_2_Moliyaviy_namuna.xlsx
+++ b/client/public/Shakl_2_Moliyaviy_namuna.xlsx
@@ -464,7 +464,7 @@
     <t>по ОКЕД</t>
   </si>
   <si>
-    <t>"O`ZAGROLIZING" AKSIYADORLIK JAMIYATI</t>
+    <t>NAMUNA KORXONA</t>
   </si>
   <si>
     <t>НЕТ ДАННЫХ В СПРАВОЧНИКЕ</t>
@@ -479,10 +479,10 @@
     <t>06244</t>
   </si>
   <si>
-    <t>ТОШКЕНТ ШАҲАР ЯККАСАРОЙ тумани</t>
-  </si>
-  <si>
-    <t>BOBUR KO`CHASI 42 А</t>
+    <t>—</t>
+  </si>
+  <si>
+    <t>—</t>
   </si>
   <si>
     <t>17.04.2026</t>
@@ -1339,9 +1339,7 @@
       <c r="H8" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="23">
-        <v>17489494</v>
-      </c>
+      <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9" ht="3.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="29"/>
@@ -1483,9 +1481,7 @@
       <c r="H18" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="24">
-        <v>203071206</v>
-      </c>
+      <c r="I18" s="24"/>
     </row>
     <row r="19" spans="1:9" ht="3.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="29"/>
@@ -1513,9 +1509,7 @@
       <c r="H20" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="I20" s="24">
-        <v>1726287</v>
-      </c>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" ht="3.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="29"/>
